--- a/datasets/ftc-staged-plan.xlsx
+++ b/datasets/ftc-staged-plan.xlsx
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -608,10 +608,10 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
@@ -644,10 +644,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
@@ -680,10 +680,10 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -716,10 +716,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
         <v>7</v>
@@ -752,10 +752,10 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
         <v>8</v>
@@ -788,10 +788,10 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
         <v>9</v>
@@ -824,10 +824,10 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
         <v>10</v>
@@ -860,10 +860,10 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
         <v>11</v>
@@ -896,10 +896,10 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
         <v>12</v>
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
         <v>12</v>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G17" t="n">
         <v>12</v>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G18" t="n">
         <v>12</v>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G19" t="n">
         <v>12</v>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F20" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G20" t="n">
         <v>12</v>
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F21" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G21" t="n">
         <v>12</v>
@@ -1141,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,20 +1247,20 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New chord V7</t>
+          <t>Inversions of I, ii, IV, V, vi</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1272,17 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New chord iii</t>
+          <t>New chord V7</t>
         </is>
       </c>
     </row>
@@ -1291,20 +1291,20 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>New key D</t>
+          <t>New chord iii</t>
         </is>
       </c>
     </row>
@@ -1313,20 +1313,20 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>New key A</t>
+          <t>Inversions of iii, V7</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>New key D</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key A</t>
         </is>
       </c>
     </row>
@@ -1382,17 +1382,17 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -1404,17 +1404,17 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -1423,20 +1423,20 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>New key F</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -1445,20 +1445,20 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key F</t>
         </is>
       </c>
     </row>
@@ -1492,17 +1492,17 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -1514,17 +1514,17 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -1533,20 +1533,20 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New key E</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -1555,20 +1555,20 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key E</t>
         </is>
       </c>
     </row>
@@ -1602,17 +1602,17 @@
         <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1624,17 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -1643,20 +1643,20 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New key B♭</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -1665,20 +1665,20 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -1690,17 +1690,17 @@
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key B♭</t>
         </is>
       </c>
     </row>
@@ -1712,17 +1712,17 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -1734,17 +1734,17 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -1753,20 +1753,20 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>New key E♭</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -1775,20 +1775,20 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1800,17 @@
         <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key E♭</t>
         </is>
       </c>
     </row>
@@ -1822,17 +1822,17 @@
         <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
         <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -1863,20 +1863,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
         <v>8</v>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>9</v>
-      </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New key A♭</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -1885,20 +1885,20 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
         <v>8</v>
       </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -1910,17 +1910,17 @@
         <v>8</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key A♭</t>
         </is>
       </c>
     </row>
@@ -1932,17 +1932,17 @@
         <v>8</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1954,17 @@
         <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -1973,20 +1973,20 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
         <v>9</v>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New key D♭</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -1995,20 +1995,20 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
         <v>9</v>
       </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -2020,17 +2020,17 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key D♭</t>
         </is>
       </c>
     </row>
@@ -2042,17 +2042,17 @@
         <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -2064,17 +2064,17 @@
         <v>9</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
         <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -2083,20 +2083,20 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
         <v>10</v>
       </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>11</v>
-      </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>New key B</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -2105,20 +2105,20 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>11</v>
-      </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -2130,17 +2130,17 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key B</t>
         </is>
       </c>
     </row>
@@ -2152,17 +2152,17 @@
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
         <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -2193,20 +2193,20 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
         <v>11</v>
       </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>12</v>
-      </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New key F♯</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -2215,20 +2215,20 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="n">
         <v>11</v>
       </c>
-      <c r="C49" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>12</v>
-      </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Adds back chord ii</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -2240,17 +2240,17 @@
         <v>11</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>12</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Adds back chord vi</t>
+          <t>New key F♯</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2262,17 @@
         <v>11</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Adds back chord V7</t>
+          <t>Adds back chord ii</t>
         </is>
       </c>
     </row>
@@ -2284,17 +2284,17 @@
         <v>11</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>12</v>
       </c>
       <c r="E52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Adds back chord iii</t>
+          <t>Adds back chord vi</t>
         </is>
       </c>
     </row>
@@ -2303,20 +2303,20 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New chord vii°</t>
+          <t>Adds back chord V7</t>
         </is>
       </c>
     </row>
@@ -2325,20 +2325,20 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Adds back key D</t>
+          <t>Adds back chord iii</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2350,17 @@
         <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Adds back key A</t>
+          <t>New chord vii°</t>
         </is>
       </c>
     </row>
@@ -2372,17 +2372,17 @@
         <v>12</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
         <v>8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Adds back key F</t>
+          <t>Inversions of vii°</t>
         </is>
       </c>
     </row>
@@ -2394,17 +2394,17 @@
         <v>12</v>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
         <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Adds back key E</t>
+          <t>Adds back key D</t>
         </is>
       </c>
     </row>
@@ -2416,17 +2416,17 @@
         <v>12</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
         <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Adds back key B♭</t>
+          <t>Adds back key A</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2438,17 @@
         <v>12</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
         <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Adds back key E♭</t>
+          <t>Adds back key F</t>
         </is>
       </c>
     </row>
@@ -2460,17 +2460,17 @@
         <v>12</v>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
         <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Adds back key A♭</t>
+          <t>Adds back key E</t>
         </is>
       </c>
     </row>
@@ -2482,17 +2482,17 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
         <v>8</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Adds back key D♭</t>
+          <t>Adds back key B♭</t>
         </is>
       </c>
     </row>
@@ -2504,17 +2504,17 @@
         <v>12</v>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
         <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Adds back key B</t>
+          <t>Adds back key E♭</t>
         </is>
       </c>
     </row>
@@ -2526,17 +2526,17 @@
         <v>12</v>
       </c>
       <c r="C63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
         <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Adds back key F♯</t>
+          <t>Adds back key A♭</t>
         </is>
       </c>
     </row>
@@ -2545,20 +2545,20 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E64" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>New chord I7, IV7, vi7, ii7, iii7, vii°7</t>
+          <t>Adds back key D♭</t>
         </is>
       </c>
     </row>
@@ -2567,20 +2567,20 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E65" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Adds back key D</t>
+          <t>Adds back key B</t>
         </is>
       </c>
     </row>
@@ -2589,20 +2589,20 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E66" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Adds back key A</t>
+          <t>Adds back key F♯</t>
         </is>
       </c>
     </row>
@@ -2614,17 +2614,17 @@
         <v>13</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
         <v>14</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Adds back key F</t>
+          <t>New chord I7, IV7, vi7, ii7, iii7, vii°7</t>
         </is>
       </c>
     </row>
@@ -2636,17 +2636,17 @@
         <v>13</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>14</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Adds back key E</t>
+          <t>Inversions of I7, ii7, iii7, IV7, vi7, vii°7</t>
         </is>
       </c>
     </row>
@@ -2658,17 +2658,17 @@
         <v>13</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
         <v>14</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Adds back key B♭</t>
+          <t>Adds back key D</t>
         </is>
       </c>
     </row>
@@ -2680,17 +2680,17 @@
         <v>13</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
         <v>14</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Adds back key E♭</t>
+          <t>Adds back key A</t>
         </is>
       </c>
     </row>
@@ -2702,17 +2702,17 @@
         <v>13</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
         <v>14</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Adds back key A♭</t>
+          <t>Adds back key F</t>
         </is>
       </c>
     </row>
@@ -2724,17 +2724,17 @@
         <v>13</v>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E72" t="n">
         <v>14</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Adds back key D♭</t>
+          <t>Adds back key E</t>
         </is>
       </c>
     </row>
@@ -2746,17 +2746,17 @@
         <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D73" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
         <v>14</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Adds back key B</t>
+          <t>Adds back key B♭</t>
         </is>
       </c>
     </row>
@@ -2768,17 +2768,17 @@
         <v>13</v>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
         <v>14</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Adds back key F♯</t>
+          <t>Adds back key E♭</t>
         </is>
       </c>
     </row>
@@ -2787,20 +2787,20 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
+        <v>13</v>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
         <v>14</v>
       </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2</v>
-      </c>
-      <c r="E75" t="n">
-        <v>21</v>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>New chord Isus4, IVsus4, Vsus4, visus4, iisus4, iiisus4, vii°sus4</t>
+          <t>Adds back key A♭</t>
         </is>
       </c>
     </row>
@@ -2809,20 +2809,20 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
+        <v>13</v>
+      </c>
+      <c r="C76" t="n">
+        <v>10</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
         <v>14</v>
       </c>
-      <c r="C76" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" t="n">
-        <v>3</v>
-      </c>
-      <c r="E76" t="n">
-        <v>21</v>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Adds back key D</t>
+          <t>Adds back key D♭</t>
         </is>
       </c>
     </row>
@@ -2831,20 +2831,20 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
+        <v>13</v>
+      </c>
+      <c r="C77" t="n">
+        <v>11</v>
+      </c>
+      <c r="D77" t="n">
+        <v>11</v>
+      </c>
+      <c r="E77" t="n">
         <v>14</v>
       </c>
-      <c r="C77" t="n">
-        <v>3</v>
-      </c>
-      <c r="D77" t="n">
-        <v>4</v>
-      </c>
-      <c r="E77" t="n">
-        <v>21</v>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Adds back key A</t>
+          <t>Adds back key B</t>
         </is>
       </c>
     </row>
@@ -2853,20 +2853,20 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
+        <v>13</v>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="n">
+        <v>12</v>
+      </c>
+      <c r="E78" t="n">
         <v>14</v>
       </c>
-      <c r="C78" t="n">
-        <v>4</v>
-      </c>
-      <c r="D78" t="n">
-        <v>5</v>
-      </c>
-      <c r="E78" t="n">
-        <v>21</v>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Adds back key F</t>
+          <t>Adds back key F♯</t>
         </is>
       </c>
     </row>
@@ -2878,17 +2878,17 @@
         <v>14</v>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>21</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Adds back key E</t>
+          <t>New chord Isus4, IVsus4, Vsus4, visus4, iisus4, iiisus4, vii°sus4</t>
         </is>
       </c>
     </row>
@@ -2900,17 +2900,17 @@
         <v>14</v>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>21</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Adds back key B♭</t>
+          <t>Inversions of Isus4, iisus4, iiisus4, IVsus4, Vsus4, visus4, vii°sus4</t>
         </is>
       </c>
     </row>
@@ -2922,17 +2922,17 @@
         <v>14</v>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>21</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Adds back key E♭</t>
+          <t>Adds back key D</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         <v>14</v>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
         <v>21</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Adds back key A♭</t>
+          <t>Adds back key A</t>
         </is>
       </c>
     </row>
@@ -2966,17 +2966,17 @@
         <v>14</v>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
         <v>21</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Adds back key D♭</t>
+          <t>Adds back key F</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
         <v>14</v>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
         <v>21</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Adds back key B</t>
+          <t>Adds back key E</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3010,17 @@
         <v>14</v>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E85" t="n">
         <v>21</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Adds back key F♯</t>
+          <t>Adds back key B♭</t>
         </is>
       </c>
     </row>
@@ -3029,20 +3029,20 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E86" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New chord Iadd9, IVadd9, Vadd9, viadd9, iiadd9, iiiadd9, vii°add9</t>
+          <t>Adds back key E♭</t>
         </is>
       </c>
     </row>
@@ -3051,20 +3051,20 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E87" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Adds back key D</t>
+          <t>Adds back key A♭</t>
         </is>
       </c>
     </row>
@@ -3073,20 +3073,20 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Adds back key A</t>
+          <t>Adds back key D♭</t>
         </is>
       </c>
     </row>
@@ -3095,20 +3095,20 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E89" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Adds back key F</t>
+          <t>Adds back key B</t>
         </is>
       </c>
     </row>
@@ -3117,20 +3117,20 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Adds back key E</t>
+          <t>Adds back key F♯</t>
         </is>
       </c>
     </row>
@@ -3142,17 +3142,17 @@
         <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
         <v>28</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Adds back key B♭</t>
+          <t>New chord Iadd9, IVadd9, Vadd9, viadd9, iiadd9, iiiadd9, vii°add9</t>
         </is>
       </c>
     </row>
@@ -3164,17 +3164,17 @@
         <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>28</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Adds back key E♭</t>
+          <t>Inversions of Iadd9, iiadd9, iiiadd9, IVadd9, Vadd9, viadd9, vii°add9</t>
         </is>
       </c>
     </row>
@@ -3186,17 +3186,17 @@
         <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
         <v>28</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Adds back key A♭</t>
+          <t>Adds back key D</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3208,17 @@
         <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E94" t="n">
         <v>28</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Adds back key D♭</t>
+          <t>Adds back key A</t>
         </is>
       </c>
     </row>
@@ -3230,17 +3230,17 @@
         <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
         <v>28</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Adds back key B</t>
+          <t>Adds back key F</t>
         </is>
       </c>
     </row>
@@ -3252,17 +3252,17 @@
         <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
         <v>28</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Adds back key F♯</t>
+          <t>Adds back key E</t>
         </is>
       </c>
     </row>
@@ -3271,20 +3271,20 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>New chord Isus2, IVsus2, Vsus2, visus2, iisus2, iiisus2, vii°sus2</t>
+          <t>Adds back key B♭</t>
         </is>
       </c>
     </row>
@@ -3293,20 +3293,20 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Adds back key D</t>
+          <t>Adds back key E♭</t>
         </is>
       </c>
     </row>
@@ -3315,20 +3315,20 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E99" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Adds back key A</t>
+          <t>Adds back key A♭</t>
         </is>
       </c>
     </row>
@@ -3337,20 +3337,20 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E100" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Adds back key F</t>
+          <t>Adds back key D♭</t>
         </is>
       </c>
     </row>
@@ -3359,20 +3359,20 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E101" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Adds back key E</t>
+          <t>Adds back key B</t>
         </is>
       </c>
     </row>
@@ -3381,20 +3381,20 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E102" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Adds back key B♭</t>
+          <t>Adds back key F♯</t>
         </is>
       </c>
     </row>
@@ -3406,17 +3406,17 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
         <v>35</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Adds back key E♭</t>
+          <t>New chord Isus2, IVsus2, Vsus2, visus2, iisus2, iiisus2, vii°sus2</t>
         </is>
       </c>
     </row>
@@ -3428,17 +3428,17 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
         <v>35</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Adds back key A♭</t>
+          <t>Inversions of Isus2, iisus2, iiisus2, IVsus2, Vsus2, visus2, vii°sus2</t>
         </is>
       </c>
     </row>
@@ -3450,17 +3450,17 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
         <v>35</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Adds back key D♭</t>
+          <t>Adds back key D</t>
         </is>
       </c>
     </row>
@@ -3472,17 +3472,17 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
         <v>35</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Adds back key B</t>
+          <t>Adds back key A</t>
         </is>
       </c>
     </row>
@@ -3494,17 +3494,17 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
         <v>35</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Adds back key F♯</t>
+          <t>Adds back key F</t>
         </is>
       </c>
     </row>
@@ -3513,20 +3513,20 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E108" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>New chord I9, IV9, V9, vi9, ii9, iii9, vii°9</t>
+          <t>Adds back key E</t>
         </is>
       </c>
     </row>
@@ -3535,20 +3535,20 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E109" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Adds back key D</t>
+          <t>Adds back key B♭</t>
         </is>
       </c>
     </row>
@@ -3557,20 +3557,20 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D110" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E110" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Adds back key A</t>
+          <t>Adds back key E♭</t>
         </is>
       </c>
     </row>
@@ -3579,20 +3579,20 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Adds back key F</t>
+          <t>Adds back key A♭</t>
         </is>
       </c>
     </row>
@@ -3601,20 +3601,20 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E112" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Adds back key E</t>
+          <t>Adds back key D♭</t>
         </is>
       </c>
     </row>
@@ -3623,20 +3623,20 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E113" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Adds back key B♭</t>
+          <t>Adds back key B</t>
         </is>
       </c>
     </row>
@@ -3645,20 +3645,20 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D114" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E114" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Adds back key E♭</t>
+          <t>Adds back key F♯</t>
         </is>
       </c>
     </row>
@@ -3670,17 +3670,17 @@
         <v>17</v>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
         <v>42</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Adds back key A♭</t>
+          <t>New chord I9, IV9, V9, vi9, ii9, iii9, vii°9</t>
         </is>
       </c>
     </row>
@@ -3692,17 +3692,17 @@
         <v>17</v>
       </c>
       <c r="C116" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
         <v>42</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Adds back key D♭</t>
+          <t>Inversions of I9, ii9, iii9, IV9, V9, vi9, vii°9</t>
         </is>
       </c>
     </row>
@@ -3714,17 +3714,17 @@
         <v>17</v>
       </c>
       <c r="C117" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D117" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E117" t="n">
         <v>42</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Adds back key B</t>
+          <t>Adds back key D</t>
         </is>
       </c>
     </row>
@@ -3736,15 +3736,191 @@
         <v>17</v>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D118" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E118" t="n">
         <v>42</v>
       </c>
       <c r="F118" t="inlineStr">
+        <is>
+          <t>Adds back key A</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>17</v>
+      </c>
+      <c r="C119" t="n">
+        <v>5</v>
+      </c>
+      <c r="D119" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" t="n">
+        <v>42</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Adds back key F</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>17</v>
+      </c>
+      <c r="C120" t="n">
+        <v>6</v>
+      </c>
+      <c r="D120" t="n">
+        <v>6</v>
+      </c>
+      <c r="E120" t="n">
+        <v>42</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Adds back key E</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>17</v>
+      </c>
+      <c r="C121" t="n">
+        <v>7</v>
+      </c>
+      <c r="D121" t="n">
+        <v>7</v>
+      </c>
+      <c r="E121" t="n">
+        <v>42</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Adds back key B♭</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>17</v>
+      </c>
+      <c r="C122" t="n">
+        <v>8</v>
+      </c>
+      <c r="D122" t="n">
+        <v>8</v>
+      </c>
+      <c r="E122" t="n">
+        <v>42</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Adds back key E♭</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>17</v>
+      </c>
+      <c r="C123" t="n">
+        <v>9</v>
+      </c>
+      <c r="D123" t="n">
+        <v>9</v>
+      </c>
+      <c r="E123" t="n">
+        <v>42</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Adds back key A♭</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>17</v>
+      </c>
+      <c r="C124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D124" t="n">
+        <v>10</v>
+      </c>
+      <c r="E124" t="n">
+        <v>42</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Adds back key D♭</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>17</v>
+      </c>
+      <c r="C125" t="n">
+        <v>11</v>
+      </c>
+      <c r="D125" t="n">
+        <v>11</v>
+      </c>
+      <c r="E125" t="n">
+        <v>42</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Adds back key B</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>17</v>
+      </c>
+      <c r="C126" t="n">
+        <v>12</v>
+      </c>
+      <c r="D126" t="n">
+        <v>12</v>
+      </c>
+      <c r="E126" t="n">
+        <v>42</v>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Adds back key F♯</t>
         </is>
@@ -8293,13 +8469,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
@@ -8332,10 +8508,10 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -8365,13 +8541,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
@@ -8404,10 +8580,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
@@ -8440,10 +8616,10 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -8476,10 +8652,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
         <v>7</v>
@@ -8512,10 +8688,10 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
         <v>8</v>
@@ -8548,10 +8724,10 @@
         <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
         <v>9</v>
@@ -8584,10 +8760,10 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
         <v>10</v>
@@ -8620,10 +8796,10 @@
         <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
         <v>11</v>
@@ -8656,10 +8832,10 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G15" t="n">
         <v>12</v>
@@ -8689,13 +8865,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G16" t="n">
         <v>12</v>
@@ -8725,13 +8901,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G17" t="n">
         <v>12</v>
@@ -8761,13 +8937,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F18" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G18" t="n">
         <v>12</v>
@@ -8797,13 +8973,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G19" t="n">
         <v>12</v>
@@ -8833,13 +9009,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F20" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G20" t="n">
         <v>12</v>
@@ -8865,7 +9041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8971,20 +9147,20 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New key B minor</t>
+          <t>Inversions of i, iv, v, VI, VII</t>
         </is>
       </c>
     </row>
@@ -8996,17 +9172,17 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>New key F♯ minor</t>
+          <t>New key B minor</t>
         </is>
       </c>
     </row>
@@ -9018,17 +9194,17 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>New key F♯ minor</t>
         </is>
       </c>
     </row>
@@ -9040,17 +9216,17 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9059,20 +9235,20 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>New chord III</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9084,17 +9260,17 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>New chord ii°</t>
+          <t>New chord III</t>
         </is>
       </c>
     </row>
@@ -9106,17 +9282,17 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Adds back key B minor</t>
+          <t>New chord ii°</t>
         </is>
       </c>
     </row>
@@ -9128,17 +9304,17 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adds back key F♯ minor</t>
+          <t>Inversions of ii°, III</t>
         </is>
       </c>
     </row>
@@ -9147,20 +9323,20 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>New key D minor</t>
+          <t>Adds back key B minor</t>
         </is>
       </c>
     </row>
@@ -9169,20 +9345,20 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back key F♯ minor</t>
         </is>
       </c>
     </row>
@@ -9194,17 +9370,17 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key D minor</t>
         </is>
       </c>
     </row>
@@ -9216,17 +9392,17 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9238,17 +9414,17 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9257,20 +9433,20 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>New key D♭ minor</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -9279,20 +9455,20 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -9304,17 +9480,17 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key D♭ minor</t>
         </is>
       </c>
     </row>
@@ -9326,17 +9502,17 @@
         <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9348,17 +9524,17 @@
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9367,20 +9543,20 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>New key G minor</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -9389,20 +9565,20 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -9414,17 +9590,17 @@
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key G minor</t>
         </is>
       </c>
     </row>
@@ -9436,17 +9612,17 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>7</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9458,17 +9634,17 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9477,20 +9653,20 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>New key C minor</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -9499,20 +9675,20 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -9524,17 +9700,17 @@
         <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key C minor</t>
         </is>
       </c>
     </row>
@@ -9546,17 +9722,17 @@
         <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9568,17 +9744,17 @@
         <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9587,20 +9763,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
         <v>8</v>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>9</v>
-      </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>New key F minor</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -9609,20 +9785,20 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="n">
         <v>8</v>
       </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>9</v>
-      </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -9634,17 +9810,17 @@
         <v>8</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
         <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key F minor</t>
         </is>
       </c>
     </row>
@@ -9656,17 +9832,17 @@
         <v>8</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
         <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9678,17 +9854,17 @@
         <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
         <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9697,20 +9873,20 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
         <v>9</v>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New key B♭ minor</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9895,20 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
         <v>9</v>
       </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -9744,17 +9920,17 @@
         <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>10</v>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key B♭ minor</t>
         </is>
       </c>
     </row>
@@ -9766,17 +9942,17 @@
         <v>9</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
         <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9788,17 +9964,17 @@
         <v>9</v>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
         <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9807,20 +9983,20 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
         <v>10</v>
       </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>11</v>
-      </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>New key A♭ minor</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -9829,20 +10005,20 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>11</v>
-      </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -9854,17 +10030,17 @@
         <v>10</v>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
         <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key A♭ minor</t>
         </is>
       </c>
     </row>
@@ -9876,17 +10052,17 @@
         <v>10</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
         <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -9898,17 +10074,17 @@
         <v>10</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
         <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -9917,20 +10093,20 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
+        <v>10</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="n">
         <v>11</v>
       </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>12</v>
-      </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New key E♭ minor</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -9939,20 +10115,20 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="n">
         <v>11</v>
       </c>
-      <c r="C49" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>12</v>
-      </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Adds back chord VI</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -9964,17 +10140,17 @@
         <v>11</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
         <v>12</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Adds back chord VII</t>
+          <t>New key E♭ minor</t>
         </is>
       </c>
     </row>
@@ -9986,17 +10162,17 @@
         <v>11</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>12</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Adds back chord III</t>
+          <t>Adds back chord VI</t>
         </is>
       </c>
     </row>
@@ -10008,17 +10184,17 @@
         <v>11</v>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
         <v>12</v>
       </c>
       <c r="E52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Adds back chord ii°</t>
+          <t>Adds back chord VII</t>
         </is>
       </c>
     </row>
@@ -10027,20 +10203,20 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E53" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New chord i7, iv7, v7, VI7, VII7, III7, ii°7</t>
+          <t>Adds back chord III</t>
         </is>
       </c>
     </row>
@@ -10049,20 +10225,20 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E54" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Adds back key B minor</t>
+          <t>Adds back chord ii°</t>
         </is>
       </c>
     </row>
@@ -10074,17 +10250,17 @@
         <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>14</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Adds back key F♯ minor</t>
+          <t>New chord i7, iv7, v7, VI7, VII7, III7, ii°7</t>
         </is>
       </c>
     </row>
@@ -10096,17 +10272,17 @@
         <v>12</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
         <v>14</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Adds back key D minor</t>
+          <t>Inversions of i7, ii°7, III7, iv7, v7, VI7, VII7</t>
         </is>
       </c>
     </row>
@@ -10118,17 +10294,17 @@
         <v>12</v>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
         <v>14</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Adds back key D♭ minor</t>
+          <t>Adds back key B minor</t>
         </is>
       </c>
     </row>
@@ -10140,17 +10316,17 @@
         <v>12</v>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
         <v>14</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Adds back key G minor</t>
+          <t>Adds back key F♯ minor</t>
         </is>
       </c>
     </row>
@@ -10162,17 +10338,17 @@
         <v>12</v>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
         <v>14</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Adds back key C minor</t>
+          <t>Adds back key D minor</t>
         </is>
       </c>
     </row>
@@ -10184,17 +10360,17 @@
         <v>12</v>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
         <v>14</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Adds back key F minor</t>
+          <t>Adds back key D♭ minor</t>
         </is>
       </c>
     </row>
@@ -10206,17 +10382,17 @@
         <v>12</v>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
         <v>14</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Adds back key B♭ minor</t>
+          <t>Adds back key G minor</t>
         </is>
       </c>
     </row>
@@ -10228,17 +10404,17 @@
         <v>12</v>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E62" t="n">
         <v>14</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Adds back key A♭ minor</t>
+          <t>Adds back key C minor</t>
         </is>
       </c>
     </row>
@@ -10250,17 +10426,17 @@
         <v>12</v>
       </c>
       <c r="C63" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D63" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
         <v>14</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Adds back key E♭ minor</t>
+          <t>Adds back key F minor</t>
         </is>
       </c>
     </row>
@@ -10269,20 +10445,20 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E64" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>New chord isus4, ivsus4, vsus4, VIsus4, VIIsus4, IIIsus4, ii°sus4</t>
+          <t>Adds back key B♭ minor</t>
         </is>
       </c>
     </row>
@@ -10291,20 +10467,20 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E65" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Adds back key B minor</t>
+          <t>Adds back key A♭ minor</t>
         </is>
       </c>
     </row>
@@ -10313,20 +10489,20 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E66" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Adds back key F♯ minor</t>
+          <t>Adds back key E♭ minor</t>
         </is>
       </c>
     </row>
@@ -10338,17 +10514,17 @@
         <v>13</v>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
         <v>21</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Adds back key D minor</t>
+          <t>New chord isus4, ivsus4, vsus4, VIsus4, VIIsus4, IIIsus4, ii°sus4</t>
         </is>
       </c>
     </row>
@@ -10360,17 +10536,17 @@
         <v>13</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>21</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Adds back key D♭ minor</t>
+          <t>Inversions of isus4, ii°sus4, IIIsus4, ivsus4, vsus4, VIsus4, VIIsus4</t>
         </is>
       </c>
     </row>
@@ -10382,17 +10558,17 @@
         <v>13</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
         <v>21</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Adds back key G minor</t>
+          <t>Adds back key B minor</t>
         </is>
       </c>
     </row>
@@ -10404,17 +10580,17 @@
         <v>13</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
         <v>21</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Adds back key C minor</t>
+          <t>Adds back key F♯ minor</t>
         </is>
       </c>
     </row>
@@ -10426,17 +10602,17 @@
         <v>13</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
         <v>21</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Adds back key F minor</t>
+          <t>Adds back key D minor</t>
         </is>
       </c>
     </row>
@@ -10448,17 +10624,17 @@
         <v>13</v>
       </c>
       <c r="C72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E72" t="n">
         <v>21</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Adds back key B♭ minor</t>
+          <t>Adds back key D♭ minor</t>
         </is>
       </c>
     </row>
@@ -10470,17 +10646,17 @@
         <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D73" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
         <v>21</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Adds back key A♭ minor</t>
+          <t>Adds back key G minor</t>
         </is>
       </c>
     </row>
@@ -10492,17 +10668,17 @@
         <v>13</v>
       </c>
       <c r="C74" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E74" t="n">
         <v>21</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Adds back key E♭ minor</t>
+          <t>Adds back key C minor</t>
         </is>
       </c>
     </row>
@@ -10511,20 +10687,20 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>New chord iadd9, ivadd9, vadd9, VIadd9, VIIadd9, IIIadd9, ii°add9</t>
+          <t>Adds back key F minor</t>
         </is>
       </c>
     </row>
@@ -10533,20 +10709,20 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E76" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Adds back key B minor</t>
+          <t>Adds back key B♭ minor</t>
         </is>
       </c>
     </row>
@@ -10555,20 +10731,20 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E77" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Adds back key F♯ minor</t>
+          <t>Adds back key A♭ minor</t>
         </is>
       </c>
     </row>
@@ -10577,20 +10753,20 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Adds back key D minor</t>
+          <t>Adds back key E♭ minor</t>
         </is>
       </c>
     </row>
@@ -10602,17 +10778,17 @@
         <v>14</v>
       </c>
       <c r="C79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>28</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Adds back key D♭ minor</t>
+          <t>New chord iadd9, ivadd9, vadd9, VIadd9, VIIadd9, IIIadd9, ii°add9</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10800,17 @@
         <v>14</v>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>28</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Adds back key G minor</t>
+          <t>Inversions of iadd9, ii°add9, IIIadd9, ivadd9, vadd9, VIadd9, VIIadd9</t>
         </is>
       </c>
     </row>
@@ -10646,17 +10822,17 @@
         <v>14</v>
       </c>
       <c r="C81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
         <v>28</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Adds back key C minor</t>
+          <t>Adds back key B minor</t>
         </is>
       </c>
     </row>
@@ -10668,17 +10844,17 @@
         <v>14</v>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E82" t="n">
         <v>28</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Adds back key F minor</t>
+          <t>Adds back key F♯ minor</t>
         </is>
       </c>
     </row>
@@ -10690,17 +10866,17 @@
         <v>14</v>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" t="n">
         <v>28</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Adds back key B♭ minor</t>
+          <t>Adds back key D minor</t>
         </is>
       </c>
     </row>
@@ -10712,17 +10888,17 @@
         <v>14</v>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
         <v>28</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Adds back key A♭ minor</t>
+          <t>Adds back key D♭ minor</t>
         </is>
       </c>
     </row>
@@ -10734,17 +10910,17 @@
         <v>14</v>
       </c>
       <c r="C85" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E85" t="n">
         <v>28</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Adds back key E♭ minor</t>
+          <t>Adds back key G minor</t>
         </is>
       </c>
     </row>
@@ -10753,20 +10929,20 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E86" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New chord isus2, ivsus2, vsus2, VIsus2, VIIsus2, IIIsus2, ii°sus2</t>
+          <t>Adds back key C minor</t>
         </is>
       </c>
     </row>
@@ -10775,20 +10951,20 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E87" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Adds back key B minor</t>
+          <t>Adds back key F minor</t>
         </is>
       </c>
     </row>
@@ -10797,20 +10973,20 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Adds back key F♯ minor</t>
+          <t>Adds back key B♭ minor</t>
         </is>
       </c>
     </row>
@@ -10819,20 +10995,20 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E89" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Adds back key D minor</t>
+          <t>Adds back key A♭ minor</t>
         </is>
       </c>
     </row>
@@ -10841,20 +11017,20 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E90" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Adds back key D♭ minor</t>
+          <t>Adds back key E♭ minor</t>
         </is>
       </c>
     </row>
@@ -10866,17 +11042,17 @@
         <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
         <v>35</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Adds back key G minor</t>
+          <t>New chord isus2, ivsus2, vsus2, VIsus2, VIIsus2, IIIsus2, ii°sus2</t>
         </is>
       </c>
     </row>
@@ -10888,17 +11064,17 @@
         <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>35</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Adds back key C minor</t>
+          <t>Inversions of isus2, ii°sus2, IIIsus2, ivsus2, vsus2, VIsus2, VIIsus2</t>
         </is>
       </c>
     </row>
@@ -10910,17 +11086,17 @@
         <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
         <v>35</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Adds back key F minor</t>
+          <t>Adds back key B minor</t>
         </is>
       </c>
     </row>
@@ -10932,17 +11108,17 @@
         <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E94" t="n">
         <v>35</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Adds back key B♭ minor</t>
+          <t>Adds back key F♯ minor</t>
         </is>
       </c>
     </row>
@@ -10954,17 +11130,17 @@
         <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
         <v>35</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Adds back key A♭ minor</t>
+          <t>Adds back key D minor</t>
         </is>
       </c>
     </row>
@@ -10976,17 +11152,17 @@
         <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E96" t="n">
         <v>35</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Adds back key E♭ minor</t>
+          <t>Adds back key D♭ minor</t>
         </is>
       </c>
     </row>
@@ -10995,20 +11171,20 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>New chord i9, iv9, v9, VI9, VII9, III9, ii°9</t>
+          <t>Adds back key G minor</t>
         </is>
       </c>
     </row>
@@ -11017,20 +11193,20 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E98" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Adds back key B minor</t>
+          <t>Adds back key C minor</t>
         </is>
       </c>
     </row>
@@ -11039,20 +11215,20 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E99" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Adds back key F♯ minor</t>
+          <t>Adds back key F minor</t>
         </is>
       </c>
     </row>
@@ -11061,20 +11237,20 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E100" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Adds back key D minor</t>
+          <t>Adds back key B♭ minor</t>
         </is>
       </c>
     </row>
@@ -11083,20 +11259,20 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E101" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Adds back key D♭ minor</t>
+          <t>Adds back key A♭ minor</t>
         </is>
       </c>
     </row>
@@ -11105,20 +11281,20 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C102" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E102" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Adds back key G minor</t>
+          <t>Adds back key E♭ minor</t>
         </is>
       </c>
     </row>
@@ -11130,17 +11306,17 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
         <v>42</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Adds back key C minor</t>
+          <t>New chord i9, iv9, v9, VI9, VII9, III9, ii°9</t>
         </is>
       </c>
     </row>
@@ -11152,17 +11328,17 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
         <v>42</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Adds back key F minor</t>
+          <t>Inversions of i9, ii°9, III9, iv9, v9, VI9, VII9</t>
         </is>
       </c>
     </row>
@@ -11174,17 +11350,17 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E105" t="n">
         <v>42</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Adds back key B♭ minor</t>
+          <t>Adds back key B minor</t>
         </is>
       </c>
     </row>
@@ -11196,17 +11372,17 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
         <v>42</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Adds back key A♭ minor</t>
+          <t>Adds back key F♯ minor</t>
         </is>
       </c>
     </row>
@@ -11218,15 +11394,169 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E107" t="n">
         <v>42</v>
       </c>
       <c r="F107" t="inlineStr">
+        <is>
+          <t>Adds back key D minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>6</v>
+      </c>
+      <c r="D108" t="n">
+        <v>6</v>
+      </c>
+      <c r="E108" t="n">
+        <v>42</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Adds back key D♭ minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>7</v>
+      </c>
+      <c r="D109" t="n">
+        <v>7</v>
+      </c>
+      <c r="E109" t="n">
+        <v>42</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Adds back key G minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>8</v>
+      </c>
+      <c r="D110" t="n">
+        <v>8</v>
+      </c>
+      <c r="E110" t="n">
+        <v>42</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Adds back key C minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>9</v>
+      </c>
+      <c r="D111" t="n">
+        <v>9</v>
+      </c>
+      <c r="E111" t="n">
+        <v>42</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Adds back key F minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>10</v>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="n">
+        <v>42</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Adds back key B♭ minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>11</v>
+      </c>
+      <c r="D113" t="n">
+        <v>11</v>
+      </c>
+      <c r="E113" t="n">
+        <v>42</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Adds back key A♭ minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" t="n">
+        <v>12</v>
+      </c>
+      <c r="E114" t="n">
+        <v>42</v>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Adds back key E♭ minor</t>
         </is>
